--- a/inspection_forms/040_hpa_operations_log_2021--inspection_forms.xlsx
+++ b/inspection_forms/040_hpa_operations_log_2021--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Assigned To Options</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By Options</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submitted_by_options</t>
+          <t>submitted_by_options_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By Options 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submitted_by_options</t>
+          <t>submitted_by_options_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By Options 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -871,7 +871,7 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1032,7 +1032,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>submitted_by_options_choices</t>
+          <t>submitted_by_options_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submitted_by_options_choices</t>
+          <t>submitted_by_options_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>submitted_by_options_choices</t>
+          <t>submitted_by_options_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submitted_by_options_choices</t>
+          <t>submitted_by_options_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
